--- a/artfynd/A 47935-2023 artfynd.xlsx
+++ b/artfynd/A 47935-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47935-2023 artfynd.xlsx
+++ b/artfynd/A 47935-2023 artfynd.xlsx
@@ -2103,10 +2103,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117771986</v>
+        <v>117771906</v>
       </c>
       <c r="B14" t="n">
-        <v>90519</v>
+        <v>90521</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589285</v>
+        <v>589367</v>
       </c>
       <c r="R14" t="n">
-        <v>6423006</v>
+        <v>6423004</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2217,10 +2217,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117771906</v>
+        <v>117771986</v>
       </c>
       <c r="B15" t="n">
-        <v>90519</v>
+        <v>90521</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589367</v>
+        <v>589285</v>
       </c>
       <c r="R15" t="n">
-        <v>6423004</v>
+        <v>6423006</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 47935-2023 artfynd.xlsx
+++ b/artfynd/A 47935-2023 artfynd.xlsx
@@ -2331,10 +2331,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118749774</v>
+        <v>118749902</v>
       </c>
       <c r="B16" t="n">
-        <v>94620</v>
+        <v>90531</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2343,31 +2343,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2375,10 +2382,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589349</v>
+        <v>589411</v>
       </c>
       <c r="R16" t="n">
-        <v>6423050</v>
+        <v>6423022</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2448,10 +2455,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118749902</v>
+        <v>118749774</v>
       </c>
       <c r="B17" t="n">
-        <v>90524</v>
+        <v>94627</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2460,38 +2467,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589411</v>
+        <v>589349</v>
       </c>
       <c r="R17" t="n">
-        <v>6423022</v>
+        <v>6423050</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 47935-2023 artfynd.xlsx
+++ b/artfynd/A 47935-2023 artfynd.xlsx
@@ -2331,10 +2331,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118749902</v>
+        <v>118749774</v>
       </c>
       <c r="B16" t="n">
-        <v>90531</v>
+        <v>94627</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2343,38 +2343,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2382,10 +2375,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589411</v>
+        <v>589349</v>
       </c>
       <c r="R16" t="n">
-        <v>6423022</v>
+        <v>6423050</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2455,10 +2448,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118749774</v>
+        <v>118749902</v>
       </c>
       <c r="B17" t="n">
-        <v>94627</v>
+        <v>90531</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2467,31 +2460,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589349</v>
+        <v>589411</v>
       </c>
       <c r="R17" t="n">
-        <v>6423050</v>
+        <v>6423022</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 47935-2023 artfynd.xlsx
+++ b/artfynd/A 47935-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113142547</v>
+        <v>118749774</v>
       </c>
       <c r="B2" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,7 +714,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589311</v>
+        <v>589349</v>
       </c>
       <c r="R2" t="n">
         <v>6423050</v>
@@ -756,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-07</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,12 +790,7 @@
         <v>113142087</v>
       </c>
       <c r="B3" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -928,15 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113142531</v>
+        <v>113142099</v>
       </c>
       <c r="B4" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,7 +941,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -975,14 +953,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 47935, Gökstad, Sm</t>
+          <t>A 49935, Gökstad, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589317</v>
+        <v>589379</v>
       </c>
       <c r="R4" t="n">
-        <v>6423006</v>
+        <v>6423002</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,6 +1003,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ska vara A 47935</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,15 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113142099</v>
+        <v>113142531</v>
       </c>
       <c r="B5" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1065,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,14 +1077,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 49935, Gökstad, Sm</t>
+          <t>A 47935, Gökstad, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589379</v>
+        <v>589317</v>
       </c>
       <c r="R5" t="n">
-        <v>6423002</v>
+        <v>6423006</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,11 +1127,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ska vara A 47935</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,12 +1157,7 @@
         <v>113142541</v>
       </c>
       <c r="B6" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1305,15 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113156909</v>
+        <v>113142547</v>
       </c>
       <c r="B7" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1356,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589345</v>
+        <v>589311</v>
       </c>
       <c r="R7" t="n">
-        <v>6423068</v>
+        <v>6423050</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1386,12 +1349,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2023-11-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,15 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113156946</v>
+        <v>113156880</v>
       </c>
       <c r="B8" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,10 +1438,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589403</v>
+        <v>589324</v>
       </c>
       <c r="R8" t="n">
-        <v>6423064</v>
+        <v>6423047</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1533,15 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113156880</v>
+        <v>113156909</v>
       </c>
       <c r="B9" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,10 +1547,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589324</v>
+        <v>589345</v>
       </c>
       <c r="R9" t="n">
-        <v>6423047</v>
+        <v>6423068</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1650,12 +1613,7 @@
         <v>113156927</v>
       </c>
       <c r="B10" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1764,12 +1722,7 @@
         <v>113156937</v>
       </c>
       <c r="B11" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1875,15 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113156952</v>
+        <v>113156946</v>
       </c>
       <c r="B12" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1858,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1926,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589411</v>
+        <v>589403</v>
       </c>
       <c r="R12" t="n">
-        <v>6423028</v>
+        <v>6423064</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1989,15 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113157022</v>
+        <v>113156952</v>
       </c>
       <c r="B13" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +1967,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2040,10 +1983,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589380</v>
+        <v>589411</v>
       </c>
       <c r="R13" t="n">
-        <v>6423010</v>
+        <v>6423028</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2103,15 +2046,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117771906</v>
+        <v>113156969</v>
       </c>
       <c r="B14" t="n">
-        <v>90523</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2138,7 +2076,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2154,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589367</v>
+        <v>589395</v>
       </c>
       <c r="R14" t="n">
-        <v>6423004</v>
+        <v>6422979</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2184,12 +2122,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2217,15 +2155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117771986</v>
+        <v>113157011</v>
       </c>
       <c r="B15" t="n">
-        <v>90523</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2252,7 +2185,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2268,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>589285</v>
+        <v>589388</v>
       </c>
       <c r="R15" t="n">
-        <v>6423006</v>
+        <v>6422985</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2298,12 +2231,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-14</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,15 +2264,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118749902</v>
+        <v>113157022</v>
       </c>
       <c r="B16" t="n">
-        <v>90533</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2366,7 +2294,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2382,10 +2310,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>589411</v>
+        <v>589380</v>
       </c>
       <c r="R16" t="n">
-        <v>6423022</v>
+        <v>6423010</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2412,22 +2340,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>08:20</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2023-11-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2455,43 +2373,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118749774</v>
+        <v>117771906</v>
       </c>
       <c r="B17" t="n">
-        <v>94632</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2499,10 +2419,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>589349</v>
+        <v>589367</v>
       </c>
       <c r="R17" t="n">
-        <v>6423050</v>
+        <v>6423004</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2529,22 +2449,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>08:20</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2569,6 +2479,449 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>117771986</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 47935, Gökstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>589285</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6423006</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118749902</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 47935, Gökstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>589411</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6423022</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118752541</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 47935, Gökstad, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>589382</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6422984</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131711428</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 11183, Ottinge, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>589081</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6423336</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
